--- a/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -719,7 +719,7 @@
     <t>Statut de l'entrée</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis|20260916095454</t>
   </si>
   <si>
     <t>Act.effectiveTime</t>

--- a/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -891,7 +891,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
+    <t xml:space="preserve">value:typeCode}
 </t>
   </si>
   <si>
@@ -7777,7 +7777,7 @@
         <v>260</v>
       </c>
       <c r="F61" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>76</v>

--- a/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
